--- a/output/pdf_financials_xlsx/TMIN.xlsx
+++ b/output/pdf_financials_xlsx/TMIN.xlsx
@@ -1980,13 +1980,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.0515</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.02036</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.183134</v>
       </c>
     </row>
     <row r="93">
@@ -2387,13 +2387,13 @@
         </is>
       </c>
       <c r="B118" s="3" t="n">
-        <v>0</v>
+        <v>-0.40957</v>
       </c>
       <c r="C118" s="3" t="n">
-        <v>0</v>
+        <v>-0.984958</v>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-0.848421</v>
       </c>
     </row>
     <row r="119">
@@ -3171,7 +3171,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>
@@ -4222,7 +4226,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr"/>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E51" s="5" t="n">
         <v>0.0515</v>
       </c>
@@ -6115,7 +6123,11 @@
           <t>Deferred exploration and evaluation expenditures 4</t>
         </is>
       </c>
-      <c r="D114" t="inlineStr"/>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
           <t>-</t>
@@ -7036,7 +7048,11 @@
           <t>Deferred exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr"/>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E145" s="5" t="n">
         <v>-0.40957</v>
       </c>

--- a/output/pdf_financials_xlsx/TMIN.xlsx
+++ b/output/pdf_financials_xlsx/TMIN.xlsx
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.008992</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.002852</v>
       </c>
     </row>
     <row r="13">
@@ -918,10 +918,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.672675</v>
+        <v>-0.681667</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.728705</v>
+        <v>-1.731557</v>
       </c>
     </row>
     <row r="28">
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.672675</v>
+        <v>-0.681667</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.728705</v>
+        <v>-1.731557</v>
       </c>
     </row>
     <row r="30">
@@ -7701,7 +7701,7 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">

--- a/output/pdf_financials_xlsx/TMIN.xlsx
+++ b/output/pdf_financials_xlsx/TMIN.xlsx
@@ -2275,13 +2275,13 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.063753</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.102116</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.010586</v>
       </c>
     </row>
     <row r="112">
@@ -2649,13 +2649,13 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.063753</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.102116</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.010586</v>
       </c>
     </row>
     <row r="135">
@@ -2665,13 +2665,13 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.635647</v>
+        <v>-0.6994</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.024828</v>
+        <v>-1.126944</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.683659</v>
+        <v>-0.694245</v>
       </c>
     </row>
   </sheetData>
@@ -6065,7 +6065,11 @@
           <t>Purchases of equipment 5</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr"/>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E112" t="inlineStr">
         <is>
           <t>-</t>
@@ -6990,7 +6994,11 @@
           <t>Purchases of equipment 6</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E143" s="5" t="n">
         <v>-0.063753</v>
       </c>
